--- a/originales/respuestas/2025/01. Calificadas/bucle p2/Alcaldía Local De Antonio Nariño.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p2/Alcaldía Local De Antonio Nariño.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Personal\Desktop\Respuesta\bucle p2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Unidades compartidas\VDLab\2025\2. Componente IIP\Etapa 3. Calificación\02. Calificadas\bucle p2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40D6C92F-595B-49A8-8657-D02506C10FDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C76F4A9-5B45-47F3-94C3-4D88E41F1776}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3E3764FF-5C7A-4E47-AB4B-04B38EE96D36}"/>
+    <workbookView xWindow="1470" yWindow="0" windowWidth="23040" windowHeight="15480" xr2:uid="{3E3764FF-5C7A-4E47-AB4B-04B38EE96D36}"/>
   </bookViews>
   <sheets>
     <sheet name="Entidad" sheetId="1" r:id="rId1"/>
@@ -680,7 +680,7 @@
         <v>23</v>
       </c>
       <c r="L2" s="5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>24</v>
